--- a/Assets/Resources/Data/Excel/StartData.xlsx
+++ b/Assets/Resources/Data/Excel/StartData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEA3335-0AC4-41F3-9251-84C5503F3059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C585A7C0-1106-403F-8C94-DCF87697EF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{B590063D-8C6E-402C-BD96-BCFCB6E3D7CD}"/>
+    <workbookView xWindow="-28920" yWindow="11385" windowWidth="29040" windowHeight="15840" xr2:uid="{B590063D-8C6E-402C-BD96-BCFCB6E3D7CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,62 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pro</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxdmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>crt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bleed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>block</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>death</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>move</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>curFloor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,11 +67,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mindmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spd</t>
+    <t>nowMP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -492,10 +432,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA0263A-A9D1-423F-AB64-DF1A05FA90CB}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -524,58 +464,13 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -598,60 +493,15 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>1013</v>
       </c>
       <c r="J2">
-        <v>90</v>
-      </c>
-      <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2">
-        <v>7</v>
-      </c>
-      <c r="O2">
-        <v>14</v>
-      </c>
-      <c r="P2">
-        <v>0.1</v>
-      </c>
-      <c r="Q2">
-        <v>0.2</v>
-      </c>
-      <c r="R2">
-        <v>0.5</v>
-      </c>
-      <c r="S2">
-        <v>0.5</v>
-      </c>
-      <c r="T2">
-        <v>0.6</v>
-      </c>
-      <c r="U2">
-        <v>0.5</v>
-      </c>
-      <c r="V2">
-        <v>0.7</v>
-      </c>
-      <c r="W2">
-        <v>0.6</v>
-      </c>
-      <c r="X2">
-        <v>10</v>
-      </c>
-      <c r="Y2">
-        <v>1013</v>
-      </c>
-      <c r="Z2" t="b">
+      <c r="K2" t="b">
         <v>0</v>
       </c>
     </row>
